--- a/data - Santiago2025/Species_traits_miss.xlsx
+++ b/data - Santiago2025/Species_traits_miss.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L152"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -412,7 +412,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Reference_BodySize_max</t>
+          <t>...12</t>
         </is>
       </c>
     </row>
@@ -653,6 +653,16 @@
           <t>Rodentia</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Echimyidae</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Myocastor</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Myocastor_coipus</t>
@@ -676,6 +686,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ursidae</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Arctotherium</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Arctotherium_tarijense</t>
@@ -702,6 +727,16 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Anatidae</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Chloephaga</t>
@@ -730,6 +765,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mephitidae</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Conepatus</t>
@@ -743,6 +788,9 @@
       <c r="F11">
         <v>1.45</v>
       </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Omnivore</t>
@@ -758,6 +806,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Canidae</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Dusicyon</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Dusicyon_avus</t>
@@ -784,6 +847,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rodentia</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cricetidae</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Euneomys</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Euneomys_chinchilloides</t>
@@ -792,6 +870,9 @@
       <c r="F13">
         <v>0.045</v>
       </c>
+      <c r="G13">
+        <v>0.06</v>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Omnivore</t>
@@ -804,6 +885,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Perissodactyla</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Equidae</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Hippidion</t>
@@ -811,7 +902,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hippidion_sp</t>
+          <t>Hippidion</t>
         </is>
       </c>
       <c r="F14">
@@ -832,6 +923,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Perissodactyla</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Equidae</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Hippidion</t>
@@ -860,6 +961,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Phocidae</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Hydrurga</t>
@@ -888,6 +999,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felidae</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Leopardus</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Leopardus_colocolo</t>
@@ -914,9 +1040,19 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>Canidae</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lycalopex</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -945,6 +1081,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Canidae</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lycalopex</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Lycalopex_griseus</t>
@@ -971,6 +1122,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mustelidae</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lyncodon</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Lyncodon_patagonicus</t>
@@ -997,6 +1163,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pilosa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mylodontidae</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Mylodon</t>
@@ -1025,6 +1201,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Otariidae</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Otaria</t>
@@ -1053,6 +1239,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Artiodactyla</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bovidae</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Ovis</t>
@@ -1081,6 +1277,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felidae</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Panthera</t>
@@ -1112,6 +1318,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Artiodactyla</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Phocoenidae</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Phocoena</t>
@@ -1119,7 +1335,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Phocoena_sp</t>
+          <t>Phocoena</t>
         </is>
       </c>
       <c r="F25">
@@ -1143,6 +1359,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felidae</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Puma_concolor</t>
@@ -1169,6 +1400,21 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felidae</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Smilodon</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Smilodon_populator</t>
@@ -1195,6 +1441,16 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sphenisciformes</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>Spheniscus</t>
@@ -1223,6 +1479,16 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Stercorariidae</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Stercorarius</t>
@@ -1230,7 +1496,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stercorarius_sp</t>
+          <t>Stercorarius</t>
         </is>
       </c>
       <c r="F29">
@@ -1254,6 +1520,16 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Anatidae</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>Tachyeres</t>
@@ -1282,6 +1558,16 @@
           <t>Mammalia</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Artiodactyla</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Camelidae</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>Vicugna</t>
@@ -1289,7 +1575,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vicugna_sp</t>
+          <t>Vicugna_vicugna</t>
         </is>
       </c>
       <c r="F31">
@@ -1310,6 +1596,16 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Suliformes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Phalacrocoracidae</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>Leucocarbo</t>
@@ -1317,7 +1613,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leucocarbo_sp</t>
+          <t>Leucocarbo</t>
         </is>
       </c>
       <c r="F32">
@@ -1338,6 +1634,16 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Laridae</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>Larus</t>
@@ -1345,7 +1651,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Larus_sp</t>
+          <t>Larus</t>
         </is>
       </c>
       <c r="F33">
@@ -1369,6 +1675,11 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Falconiformes</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>Falconidae</t>
@@ -1400,6 +1711,11 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>Anatidae</t>
@@ -1428,6 +1744,11 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rheiformes</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>Rheidae</t>
@@ -1456,27 +1777,35 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Podicipediformes</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Anatidae</t>
+          <t>Podicipedidae</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lophonetta</t>
+          <t>Podiceps</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lophonetta_specularioides</t>
+          <t>Podiceps_major</t>
         </is>
       </c>
       <c r="F37">
-        <v>1</v>
+        <v>1.2</v>
+      </c>
+      <c r="G37">
+        <v>1.6</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Herbivore</t>
+          <t>Piscivore</t>
         </is>
       </c>
     </row>
@@ -1486,814 +1815,3514 @@
           <t>Aves</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sphenisciformes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Eudyptes</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Eudyptes_chrysocome</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>2.3</v>
+      </c>
+      <c r="G38">
+        <v>4.3</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>los que comen crustaceos y peces hay que decidir qué son</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sphenisciformes</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Aptenodytes</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aptenodytes_patagonicus</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G39">
+        <v>17.3</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Piscivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sphenisciformes</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Aptenodytes</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aptenodytes cfr. Forsteri</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>19</v>
+      </c>
+      <c r="G40">
+        <v>46</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Piscivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sphenisciformes</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pygoscelis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pygoscelis_papua</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>4.5</v>
+      </c>
+      <c r="G41">
+        <v>8.5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Stercorariidae</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Catharacta</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Catharacta_ skua</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>1.1</v>
+      </c>
+      <c r="G42">
+        <v>1.7</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pelecaniformes</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ardeidae</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ardea</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ardea_cocoi</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>1.9</v>
+      </c>
+      <c r="G43">
+        <v>2.1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Piscivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Charadriidae</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Vanellus</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Vanellus_chilensis</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>0.246</v>
+      </c>
+      <c r="G44">
+        <v>0.285</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Strigiformes</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tytonidae</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tyto</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Tyto_alba</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>0.187</v>
+      </c>
+      <c r="G45">
+        <v>0.455</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Strigiformes</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Strigidae</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bubo</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Bubo_magellanicus</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="G46">
+        <v>1.5</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pelecaniformes</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Threskiornithidae</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Theristicus</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Theristicus_caudatus</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>1.466</v>
+      </c>
+      <c r="G47">
+        <v>1.55</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Insectivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Accipitriformes</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Accipitridae</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Accipiter</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Accipiter_bicolor</t>
+        </is>
+      </c>
+      <c r="F48">
+        <v>0.207</v>
+      </c>
+      <c r="G48">
+        <v>0.4</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Falconiformes</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Falconidae</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Milvago</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Milvago_chimango</t>
+        </is>
+      </c>
+      <c r="F49">
+        <v>0.289</v>
+      </c>
+      <c r="G49">
+        <v>0.3</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Accipitriformes</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Accipitridae</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Geranoaetus</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Geranoaetus_polyosoma</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>0.66</v>
+      </c>
+      <c r="G50">
+        <v>1.3</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Accipitriformes</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Accipitridae</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Geranoaetus</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Geranoaetus_melanoleucus</t>
+        </is>
+      </c>
+      <c r="F51">
+        <v>1.67</v>
+      </c>
+      <c r="G51">
+        <v>3.17</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Falconiformes</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Falconidae</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Caracara</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Caracara_plancus</t>
+        </is>
+      </c>
+      <c r="F52">
+        <v>1.15</v>
+      </c>
+      <c r="G52">
+        <v>1.6</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Procellariiformes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Diomedeidae</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thalassarche</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Thalassarche_melanophris</t>
+        </is>
+      </c>
+      <c r="F53">
+        <v>2.84</v>
+      </c>
+      <c r="G53">
+        <v>4.658</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Piscivore</t>
+        </is>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Galliformes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Phasianidae</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gallus</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Gallus_gallus_domesticus</t>
+        </is>
+      </c>
+      <c r="F54">
+        <v>0.485</v>
+      </c>
+      <c r="G54">
+        <v>1.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Strigiformes</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Strigidae</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Strix</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Strix_rufipes</t>
+        </is>
+      </c>
+      <c r="F55">
+        <v>0.3</v>
+      </c>
+      <c r="G55">
+        <v>0.5</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Piciformes</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Picidae</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Campephilus</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Campephilus_magellanicus</t>
+        </is>
+      </c>
+      <c r="F56">
+        <v>0.276</v>
+      </c>
+      <c r="G56">
+        <v>0.363</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Insectivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Suliformes</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Phalacrocoracidae</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Phalacrocorax</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Phalacrocorax_magellanicus</t>
+        </is>
+      </c>
+      <c r="F57">
+        <v>1.72</v>
+      </c>
+      <c r="G57">
+        <v>2.72</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Piscivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Suliformes</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Phalacrocoracidae</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Leucocarbo</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Leucocarbo_atriceps</t>
+        </is>
+      </c>
+      <c r="F58">
+        <v>1.72</v>
+      </c>
+      <c r="G58">
+        <v>2.3</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Piscivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Laridae</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Larus</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Larus_maculipennis</t>
+        </is>
+      </c>
+      <c r="F59">
+        <v>0.28</v>
+      </c>
+      <c r="G59">
+        <v>0.36</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pelecaniformes</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ardeidae</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nycticorax</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Nycticorax_nycticorax</t>
+        </is>
+      </c>
+      <c r="F60">
+        <v>0.278</v>
+      </c>
+      <c r="G60">
+        <v>1.1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Procellariiformes</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Diomedeidae</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Diomedea</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Diomedea_melanophris</t>
+        </is>
+      </c>
+      <c r="F61">
+        <v>2.84</v>
+      </c>
+      <c r="G61">
+        <v>4.658</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>es el mismo que Thalassarche melanophris</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Procellariiformes</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Procellariidae</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Macronectes</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Macronectes_giganteus</t>
+        </is>
+      </c>
+      <c r="F62">
+        <v>3.8</v>
+      </c>
+      <c r="G62">
+        <v>5</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Anatidae</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Anas</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Anas_flavirostris</t>
+        </is>
+      </c>
+      <c r="F63">
+        <v>0.388</v>
+      </c>
+      <c r="G63">
+        <v>0.83</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Anatidae</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Anas</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Anas_specularioides</t>
+        </is>
+      </c>
+      <c r="F64">
+        <v>0.9</v>
+      </c>
+      <c r="G64">
+        <v>1.4</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>actualmente Lophonetta specularoides</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Anatidae</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Anas</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Anas_georgica</t>
+        </is>
+      </c>
+      <c r="F65">
+        <v>0.46</v>
+      </c>
+      <c r="G65">
+        <v>0.655</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Thinocoridae</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Attagis</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Attagis_malouinus</t>
+        </is>
+      </c>
+      <c r="F66">
+        <v>0.308</v>
+      </c>
+      <c r="G66">
+        <v>0.35</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Strigiformes</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Strigidae</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Asio</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Asio_flammeus</t>
+        </is>
+      </c>
+      <c r="F67">
+        <v>0.206</v>
+      </c>
+      <c r="G67">
+        <v>0.363</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Procellariiformes</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Procellariidae</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Macronectes</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Macronectes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sphenisciformes</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Eudyptes</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Eudyptes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sphenisciformes</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Spheniscidae</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Suliformes</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Phalacrocoracidae</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Phalacrocoracidae</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Piscivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Anatidae</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Chloephaga</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Chloephaga</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Laridae</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Laridae</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Strigiformes</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Strigiformes</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Accipitriformes</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Accipitridae</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Accipitridae</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Procellariiformes</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Diomedeidae</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Diomedea</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Diomedea</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Passeriformes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Passeriformes</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Haematopodidae</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Haematopodidae</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Procellariiformes</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Procellariiformes</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Laridae</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Larus</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Larus_dominicanus</t>
+        </is>
+      </c>
+      <c r="F81">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G81">
+        <v>1.335</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Anseriformes</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Anatidae</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lophonetta</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Lophonetta_specularioides</t>
+        </is>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>1.2</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>está arriba como Anas specularoides</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Aves</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Charadriiformes</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sternidae</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sterna</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Sterna_hirundinacea</t>
         </is>
       </c>
-      <c r="F38">
+      <c r="F83">
         <v>0.2</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="G83">
+        <v>0.3</v>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>Piscivore</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="E39" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pinnipedia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Rodentia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cricetidae</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Abrothrix</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Abrothrix_hirta</t>
+        </is>
+      </c>
+      <c r="F85">
+        <v>0.02</v>
+      </c>
+      <c r="G85">
+        <v>0.022</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Rodentia</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cricetidae</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Abrothrix</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Abrothrix_olivacea</t>
+        </is>
+      </c>
+      <c r="F86">
+        <v>0.012</v>
+      </c>
+      <c r="G86">
+        <v>0.024</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Felidae</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Panthera</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Panthera_onca_mesembrina</t>
+        </is>
+      </c>
+      <c r="F87">
+        <v>50</v>
+      </c>
+      <c r="G87">
+        <v>129</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Rodentia</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cricetidae</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Reithrodon</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Reithrodon_auritus</t>
+        </is>
+      </c>
+      <c r="F88">
+        <v>0.052</v>
+      </c>
+      <c r="G88">
+        <v>0.116</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Otariidae_x000D_</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Arctocephalus</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Arctocephalus_australis</t>
+        </is>
+      </c>
+      <c r="F89">
+        <v>40</v>
+      </c>
+      <c r="G89">
+        <v>160</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Phocidae</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mirounga</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Mirounga_leonina</t>
+        </is>
+      </c>
+      <c r="F90">
+        <v>400</v>
+      </c>
+      <c r="G90">
+        <v>3996</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Cetartiodactyla</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Balaenopteridae</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Balaenoptera</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Balaenoptera_borealis</t>
+        </is>
+      </c>
+      <c r="F91">
+        <v>20000</v>
+      </c>
+      <c r="G91">
+        <v>22000</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cetartiodactyla</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Physeteridae</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Physeter</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Physeter_macrocephalus</t>
+        </is>
+      </c>
+      <c r="F92">
+        <v>20000</v>
+      </c>
+      <c r="G92">
+        <v>50000</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Cetartiodactyla</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Delphinidae</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Grampus</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Grampus_griseus</t>
+        </is>
+      </c>
+      <c r="F93">
+        <v>380</v>
+      </c>
+      <c r="G93">
+        <v>500</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Artiodactyla</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Bovidae</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Bos</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Bos_taurus</t>
+        </is>
+      </c>
+      <c r="F94">
+        <v>400</v>
+      </c>
+      <c r="G94">
+        <v>1000</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Artiodactyla</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Camelidae</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Camelidae</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Rodentia</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Rodentia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Omnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Lagomorpha</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Lagomorpha</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Mustelidae</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lontra</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Lontra</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Canidae</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Canidae</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Carnivora</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Phocidae</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Phocidae</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Artiodactyla</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Delphinidae</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Delphinidae</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Mammalia</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Artiodactyla</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Cetacea</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Carnivore</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Mytiloida</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Mytilidae</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Mytilus</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t>Mytilus_chilensis</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="E40" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Mytiloida</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mytilidae</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Aulacomya</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>Aulacomya_atra</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="E41" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Muricidae</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Acanthina</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Acanthina_monodon</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Neogastropoda</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Muricidae</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Trophon</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Trophon_geversianus</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Veneroida</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Mactridae</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Mulinia</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Mulinia_edulis</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Venerida</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Veneridae</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ameghinomya</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Ameghinomya_antiqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Mytilida</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Mytilidae</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Brachidontes</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Brachidontes_purpuratus</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Buccinanopsidae</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Buccinanops</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Buccinanops_squalidus</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Buccinanopsidae</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Buccinanops</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Buccinanops_globulosus</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Neogastropoda</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Cominellidae</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Paraheutria</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Paraheutria_ plumbea</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Venerida</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Veneridae</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Eurhomalea</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Eurhomalea_exalbida</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Bivalvia</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Venerida</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Veneridae</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Venus</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Venus_antiqua</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Echinoidea</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Echinoida</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Echinidae</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Loxechinus</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Loxechinus_albus</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chilinidae</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Chillina</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Chillina_patagonica</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Neogastropoda</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Volutidae</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Odontocimbiola</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Odontocimbiola</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Nacellidae</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Nacella</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Nacella</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Neogastropoda</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Volutidae</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Adelomelon</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Adelomelon</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Gastropoda</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Fissurellidae</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Fissurella</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Fissurella</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Polyplacophora</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Chitonidae</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Chitonidae</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Thecostraca</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sessilia</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Balanidae</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Balanus</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Balanus</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ophidiiformes</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ophidiidae</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Genypterus</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Genypterus_blacodes</t>
+        </is>
+      </c>
+      <c r="F123">
+        <v>10</v>
+      </c>
+      <c r="G123">
+        <v>20</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php;</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Bovichtidae</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Cottoperca</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Cottoperca_gobio</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Eleginopsidae</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Eleginops</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Eleginops_maclovinus</t>
+        </is>
+      </c>
+      <c r="F125">
+        <v>0.052</v>
+      </c>
+      <c r="G125">
+        <v>1.57</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Muñoz, G. M., Ruiz, A. E., Fondacaro, R. R., Carbajo, A., &amp; Sanchez, L. M. (2019). Estudio del róbalo, Eleginops maclovinus, en aguas del sistema costero playa Magagna, Patagonia Norte, Argentina.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Muñoz, G. M., Ruiz, A. E., Fondacaro, R. R., Carbajo, A., &amp; Sanchez, L. M. (2019). Estudio del róbalo, Eleginops maclovinus, en aguas del sistema costero playa Magagna, Patagonia Norte, Argentina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Gadiformes</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Merlucciidae</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Macruronus</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Macruronus_magellanicus</t>
+        </is>
+      </c>
+      <c r="F126">
+        <v>0.5</v>
+      </c>
+      <c r="G126">
+        <v>5</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php;</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gempylidae</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Thyrsites</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Thyrsites_atun</t>
+        </is>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127">
+        <v>5</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php;</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Gadiformes</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Moridae</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Salilota</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Salilota_australis</t>
+        </is>
+      </c>
+      <c r="F128">
+        <v>100</v>
+      </c>
+      <c r="G128">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Scorpaeniformes</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Sebastidae</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sebastes</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Sebastes_oculatus</t>
+        </is>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>3</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>on line</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Clupeiformes</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Clupeidae</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Sprattus</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Sprattus_fueguensis</t>
+        </is>
+      </c>
+      <c r="F130">
+        <v>0.04</v>
+      </c>
+      <c r="G130">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gadiformes</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Gadidae</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Micromesistius</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Micromesistius_australis</t>
+        </is>
+      </c>
+      <c r="F131">
+        <v>0.7</v>
+      </c>
+      <c r="G131">
+        <v>0.85</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php;</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Nototheniidae</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Paranotothenia</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Paranotothenia_magellanica</t>
+        </is>
+      </c>
+      <c r="F132">
+        <v>0.5</v>
+      </c>
+      <c r="G132">
+        <v>1.5</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php;</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Serranidae</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Serranus</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Serranus_capensis</t>
+        </is>
+      </c>
+      <c r="F133">
+        <v>0.1</v>
+      </c>
+      <c r="G133">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Zoarcidae</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Austrolycus</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Austrolycus</t>
+        </is>
+      </c>
+      <c r="F134">
+        <v>0.714</v>
+      </c>
+      <c r="G134">
+        <v>6.163</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Gadiformes</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Merluciidae</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Merluciidae</t>
+        </is>
+      </c>
+      <c r="F135">
+        <v>1.5</v>
+      </c>
+      <c r="G135">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Teleostei</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Atheriniformes</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Atherinopsidae</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Odontesthes</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Odontesthes</t>
+        </is>
+      </c>
+      <c r="F136">
+        <v>0.26</v>
+      </c>
+      <c r="G136">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Nototheniidae</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Nototheniidae</t>
+        </is>
+      </c>
+      <c r="F137">
+        <v>0.101</v>
+      </c>
+      <c r="G137">
+        <v>0.346</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php;</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>https://www.fishbase.se/search.php;</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Actinopterygii</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Perciformes</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Nototheniidae</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Patagonotothen</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Patagonotothen</t>
+        </is>
+      </c>
+      <c r="F138">
+        <v>0.0015</v>
+      </c>
+      <c r="G138">
+        <v>0.0039</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Chondrichthyes</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="E140" t="inlineStr">
         <is>
           <t>Tegula_atra</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Acanthina_monodon</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="E43" t="inlineStr">
+    <row r="141">
+      <c r="E141" t="inlineStr">
         <is>
           <t>Trophon_gervesianus</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Mulinia_edulis</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Ameghinomya_antiqua</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Brachidontes_purpuratus</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Buccinanops_squalidus</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Buccinanops_globulosus</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Paraheutria_ plumbea</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Eurhomalea_exalbida</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Venus_antiqua</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Loxechinus_albus</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Chillina_patagonica</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="E54" t="inlineStr">
+    <row r="142">
+      <c r="E142" t="inlineStr">
         <is>
           <t>Odontocimbiola sp.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="E55" t="inlineStr">
+    <row r="143">
+      <c r="E143" t="inlineStr">
         <is>
           <t>Nacella spp.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Adelomelon</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Fissurella</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Chitonidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="E59" t="inlineStr">
+    <row r="144">
+      <c r="E144" t="inlineStr">
         <is>
           <t>Balanus sp.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Genypterus_blacodes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Cottoperca_gobio</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Eleginops_maclovinus</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Macruronus_magellanicus</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Thyrsites_atun</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Salilota_australis</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Sebastes_oculatus</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Sprattus_fueguensis</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Micromesistius_australis</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Paranotothenia_magellanica</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Serranus_capensis</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="E71" t="inlineStr">
+    <row r="145">
+      <c r="E145" t="inlineStr">
         <is>
           <t>Austrolycus sp.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Merluciidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Odontesthes</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Nototheniidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Patagonotothen</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Bos_taurus</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="E78" t="inlineStr">
+    <row r="146">
+      <c r="E146" t="inlineStr">
         <is>
           <t>Ctenomys_megellanicus</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Abrothrix_olivacea</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Abrothrix_hirta</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Vicugna_vicugna</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="E82" t="inlineStr">
+    <row r="147">
+      <c r="E147" t="inlineStr">
         <is>
           <t>Mylodon_darwini</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="E83" t="inlineStr">
+    <row r="148">
+      <c r="E148" t="inlineStr">
         <is>
           <t>Pseudalopex_culpaeus</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="E84" t="inlineStr">
+    <row r="149">
+      <c r="E149" t="inlineStr">
         <is>
           <t xml:space="preserve">Panthera_onca_mesembrina
 </t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Reithrodon_auritus</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Arctocephalus_australis</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Mirounga_leonina</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Balaenoptera_borealis</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Physeter_macrocephalus</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Grampus_griseus</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Camelidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Artiodactyla</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Lagomorpha</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Lontra</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Rodentia</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Canidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Phocidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Delfinidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Cetacea</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Phocoena</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Mammalia_megafauna</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Theristicus_caudatus</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Podiceps_major</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Eudyptes_chrysocome</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Aptenodytes_patagonicus</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Aptenodytes cfr. Forsteri</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Pygoscelis_papua</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Catharacta_skua</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Ardea_cocoi</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Vanellus_chilensis</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Tyto_alba</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Bubo_magellanicus</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Accipiter_bicolor</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Milvago_chimango</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Geranoaetus_polyosoma</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Geranoaetus_melanoleucus</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Caracara_plancus</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Thalassarche_melanophris</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Gallus_gallus_domesticus</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Strix_rufipes</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Campephilus_magellanicus</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Phalacrocorax_magellanicus</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Leucocarbo_atriceps</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Larus_dominicanus</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Larus_maculipennis</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Nycticorax_nycticorax</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Diomedea-melanophris</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Macronectes_giganteus</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Anas_flavirostris</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Anas_specularioides</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Anas_georgica</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Attagis_malouinus</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Asio_flammeus</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Stercorarius sp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Macronectes</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Eudyptes</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Spheniscidae</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Strigiforme</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Accipitridae</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Charadriiformes</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Diomedea</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Passeriformes</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Procellariiformes</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Haematopus</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Ave_indet</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Indet_indet</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Chloephaga sp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Laridae</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Pinnipedia</t>
-        </is>
-      </c>
-    </row>
     <row r="150">
       <c r="E150" t="inlineStr">
         <is>
-          <t>Phalacrocoracidae</t>
+          <t>Artiodactyla</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="E151" t="inlineStr">
         <is>
-          <t>Mammalia_indet</t>
+          <t>Delfinidae</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="E152" t="inlineStr">
+        <is>
+          <t>Mammalia_megafauna</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Catharacta_skua</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Diomedea-melanophris</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Stercorarius sp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Strigiforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Haematopus</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Ave_indet</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Indet_indet</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Chloephaga sp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Mammalia_indet</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="E162" t="inlineStr">
         <is>
           <t>Peces_Indet</t>
         </is>
